--- a/human_validation/judge/kor/judge_D005_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S003_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,303 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 직장에서 이상한 일들이 생기기 시작해서 왔어요, 사람들도 놀랄 정도로요. 저는 웨이트리스인데, 서비스 도중에 갑자기 얼어붙곤 해요. 그러니까, 탄산수 스테이션 옆에 서서 계산대 열쇠를 든 채로 계산서를 정리하는 대신 테이블 번호만 계속 반복해서 말하고 있거나요. 아니면 순서를 완전히 틀리게 하고 그걸 바로 알아차리지도 못해요. 설명하기가 힘들었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 다른 사람들은 눈치채지 못하는 것을 보거나 듣거나 느낀 적이 있나요, 아니면 다른 사람들이 사실이 아니라고 하는데도 뭔가를 강하게 믿은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네… 뭔가를 듣긴 했어요. 항상 그런 건 아닌데, 가끔 직장에서 마감할 때나 집 부엌에 있을 때, 어떤 여자 목소리가 제 이름을 부르는 걸 들어요. 가끔은 제가 계산을 잘못하고 있다고 말하기도 해요. 소리가 꽤 또렷해서 대답을 하게 되는데, 그러고 나서야 다른 사람은 아무것도 못 들었다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다른 사람들이 명확한 증거를 줬는데도 뭔가를 사실이라고 믿었던 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 직장에서 서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 생각이 계속 들어요. 마치 제가 실수하는지 확인하는 것처럼요. 가끔 영수증에 표시나 변경된 흔적이 보이면 그게 저를 해고시키려고 남기는 작은 신호처럼 느껴져요. 남편은 그냥 평범한 식당 착오일 뿐이라고 하는데, 그래도 뭔가 의미가 있는 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 특별히 스트레스를 받거나 화가 난 상태가 아닐 때도 이런 목소리나 믿음을 경험한 적이 있나요, 그리고 그런 일들이 그때 일어나는 일과 상관없이 저절로 일어나는 것처럼 느껴지기도 하나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 가끔은 뭔가 큰 일이랑 연결돼 있는 것 같지 않을 때도 있어요. 그냥 직장에서 마감할 때나 집 부엌에 있을 때, 특별히 화가 난 상태도 아닌데 그럴 수 있어요. 여자 목소리가 제 이름을 부르거나, 계산이 틀렸다고 말하는 게 들리는데, 진짜처럼 들려서 대답을 하고 나서야 아무도 못 들었다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 사실이 아니라는 걸 알면서도, 그렇게 생각할 이유가 없는데도, 그리고 그 믿음이 본인의 삶에서 일어나는 일과 연결되지 않는데도 뭔가를 믿은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네… 직장 관련된 일이 그런 것 같아요. 서버 몇 명이랑 이 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 느낌이 계속 들어요, 마치 실수를 찾는 것처럼요.
+그리고 영수증에 표시가 있거나 뭔가 바뀐 것 같으면, 그게 신호를 남기는 것처럼, 저를 해고시키려는 증거처럼 느껴져요. 남편은 그냥 평범한 식당 실수일 뿐이라고 하고, 저도 그 말이 이해는 되는데, 그래도 그 순간엔 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 특별히 우울하거나 불안하거나 화가 나지 않았을 때 이런 생각이나 믿음이 들었던 때를 떠올릴 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 딱히 화가 나지 않았던, 꽤 평범한 날에도 직장에서 그런 일이 있었어요. 그냥 주문을 입력하고 있는데, 서버 몇 명이랑 그 단골손님이 저를 지켜보고 있는 것 같은 느낌이 들기 시작해요, 제가 실수하기를 기다리는 것처럼요.
+그러고 나서 영수증에 표시가 있거나 뭔가 바뀐 것 같으면, 그걸 저를 위해 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여요. 남편은 그냥 평범한 식당 혼선일 뿐이라고 하는데, 그 순간에는 여전히 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 전혀 증거가 없는데도 다른 사람들이 이상하다거나 이해하기 힘들다고 여길 만한 것을 믿은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 이상하게 들릴 거란 건 아는데, 서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 계속 지켜보고 있다는 생각이 들어요.
+영수증에 작은 표시가 있거나 뭔가 바뀐 것 같으면, 그걸 저한테 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여요. 남편은 그냥 평범한 식당 착오일 뿐이라고 하고, 왜 그렇게 말하는지 이해는 가는데, 막상 그 일이 일어날 때는 저한테는 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 대부분의 사람들이 매우 이상하거나 불가능하다고 여길 만한, 현실에 전혀 근거가 없는 것을 믿은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 그러니까… 외계인 같은 불가능한 얘기는 아닌데, 말로 꺼내놓고 보면 근거가 별로 없다는 느낌은 들어요.
+서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 느낌이 계속 들어요. 그리고 영수증에 작은 표시가 있거나 뭔가 바뀐 것 같으면, 저를 위해 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여요.
+남편은 그냥 평범한 식당 실수나 혼선일 뿐이라고 하고, 그게 더 말이 된다는 것도 알아요. 근데 제가 그 자리에 있을 때는 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 우울하거나 불안하거나 화가 난 상태가 전혀 아닐 때도 사람들이 지켜보고 있다거나 해고시키려 한다는 이런 믿음을 가진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 전혀 우울하거나 불안하거나 그런 상태가 아닐 때도 일어나요. 그러니까 직장에서 평범한 근무를 하다가도, 서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 느낌이 여전히 들어요.
+그러고 나서 영수증에 작은 표시가 있거나 뭔가 이상해 보이면, 그게 저를 위해 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여져요. 남편은 그냥 평범한 식당 혼선일 뿐이라고 하고, 아마 사실일 거란 것도 아는데, 그 순간에는 여전히 그걸 믿게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 다른 사람들이 이런 신호를 눈치채지 못하고 남편분도 그냥 평범한 식당 실수일 뿐이라고 논리적으로는 이해하면서도, 마음속 깊은 곳에서는 여전히 본인의 믿음이 절대적으로 사실이고 의심의 여지가 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네… 그 일이 일어나고 있을 때는 마음속 깊은 곳에서 여전히 그게 사실이라고 느끼는 것 같아요.
+남편이 그냥 평범한 식당 일일 뿐이라고 하는 걸 들을 수 있고, 마음 한편으로는 그게 말이 된다는 것도 알아요. 근데 직장에서 영수증에 표시가 있거나 뭔가 바뀐 걸 볼 때는, 일부러 그러는 것처럼 느껴져요—서버들이랑 그 단골손님이 저를 지켜보면서 해고당하도록 몰아가려는 것처럼요. 증명은 못 해도 그냥 넘기기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 사실이 아니라는 명백한 증거를 본 후에도 이런 믿음 중 하나를 계속 붙들고 있었던 때를 떠올릴 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 한번은 서버 중 한 명이 제가 어떻게 주문을 입력하는지 추적하려고 다른 사람들에게 경고하기 위해 영수증에 표시를 했다고 생각한 적이 있어요.
+나중에 남편이 그걸 보더니 그냥 평범한 실수라고, 누가 낙서를 했거나 주문 때문에 뭔가 바꾼 거라고 했어요. 그리고 저도 남편이 무슨 말을 하는지는 이해했어요. 사실 그건 아무것도 증명하지 못했어요.
+근데 그 후에도 저는 계속 생각했어요, 아니야, 그 표시는 이유가 있어서 거기 있었던 거야. 여전히 저를 해고시키려고 몰아가려는 것 같았어요. 한번 눈치채고 나면 그걸 놓아버리기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 영수증의 표시가 그냥 평범한 실수였다는 걸 본 후에도, 그게 실제로 서버들이 본인을 해고시키기 위한 비밀 신호라고 여전히 확신했고, 그 순간에는 다른 설명을 받아들일 수 없었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 그냥 평범한 실수였을 수도 있다는 걸 알아본 후에도, 여전히 뭔가 의미가 있다고 느꼈어요.
+그때는 그게 정말 아무것도 아니라는 걸 받아들일 수가 없었어요. 계속 서버들이 영수증에 그런 작은 신호들을 남기고 있고, 그 단골손님도 지켜보고 있다는 생각이 들었어요, 마치 다들 제가 뭔가 잘못하는 걸 잡아서 해고시키려는 것처럼요. 남편이 평범한 일이라고 말해준 것도 그 생각을 딱히 없애주지는 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 영수증의 표시가 아마도 그냥 평범한 실수였다는 걸 본 후에도, 그게 실제로 서버들이 남긴 비밀 신호라고 여전히 완전히 확신했고, 그게 그냥 사고였을 수도 있다는 게 불가능하게 느껴졌나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네… 그때는 정말 그게 그냥 사고일 수는 없다고 느껴졌어요.
+남편이 아마 그냥 평범한 식당 혼선일 거라고 말했을 때도, 저는 여전히 그 표시가 뭔가 의미가 있다고 확신했어요. 서버들이 영수증에 신호를 남기고 있고, 그 단골손님도 제가 주문 입력하는 걸 지켜보면서 제가 해고당하게 만들려고 뭔가를 증명하려는 것 같았어요. 얘기하고 보니 좀 과하게 들리는 건 아는데, 그 순간에는 저한테 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현병 (D005)
 인구통계: 성별 여성 / 나이 32 / 직업상태 waiter or waitress / 최종학력 대학 재학
@@ -575,352 +863,34 @@
 증상 지속 기간: 1 year and 2 months
 추가 요건: 
 주호소 증상 코드: S022
-배경 서술: 코리나가 서브세이프 매니저 자격증을 준비하면서 저녁 근무 조 팀장을 맡아달라는 요청을 받았을 때, 그 추가된 책임은 평소 여유롭던 식당 업무 루틴을 끊임없는 압박의 원천으로 바꿔 놓았다. 이후 1년 2개월에 걸쳐, 동료와 손님에 대한 초기의 다소 이상한 우려는 고정된 믿음으로 굳어졌고, 그녀는 다른 사람들이 확인할 수 없는 경험에 반응하기 시작했으며, 서비스 도중 행동이 흐트러져 주문, 현금 처리, 마감 절차에 지장을 줄 정도가 되었다. 집에서는 남편이 그녀가 위축되고 의욕을 잃으면서 해변 산책, 정원 가꾸기, 베이킹, 일기 쓰기가 점점 줄어드는 것을 알아챘다. 그녀는 매니저 평가에 실패하고 고용주와의 면담에서 직장과 결혼 생활을 지키기 위해 긴급 외래 평가에 동의한 뒤 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 직장에서 이상한 일들이 생기기 시작해서 왔어요, 사람들도 놀랄 정도로요. 저는 웨이트리스인데, 서비스 도중에 갑자기 얼어붙곤 해요. 그러니까, 탄산수 스테이션 옆에 서서 계산대 열쇠를 든 채로 계산서를 정리하는 대신 테이블 번호만 계속 반복해서 말하고 있거나요. 아니면 순서를 완전히 틀리게 하고 그걸 바로 알아차리지도 못해요. 설명하기가 힘들었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 다른 사람들은 눈치채지 못하는 것을 보거나 듣거나 느낀 적이 있나요, 아니면 다른 사람들이 사실이 아니라고 하는데도 뭔가를 강하게 믿은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네… 뭔가를 듣긴 했어요. 항상 그런 건 아닌데, 가끔 직장에서 마감할 때나 집 부엌에 있을 때, 어떤 여자 목소리가 제 이름을 부르는 걸 들어요. 가끔은 제가 계산을 잘못하고 있다고 말하기도 해요. 소리가 꽤 또렷해서 대답을 하게 되는데, 그러고 나서야 다른 사람은 아무것도 못 들었다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다른 사람들이 명확한 증거를 줬는데도 뭔가를 사실이라고 믿었던 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 직장에서 서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 생각이 계속 들어요. 마치 제가 실수하는지 확인하는 것처럼요. 가끔 영수증에 표시나 변경된 흔적이 보이면 그게 저를 해고시키려고 남기는 작은 신호처럼 느껴져요. 남편은 그냥 평범한 식당 착오일 뿐이라고 하는데, 그래도 뭔가 의미가 있는 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 특별히 스트레스를 받거나 화가 난 상태가 아닐 때도 이런 목소리나 믿음을 경험한 적이 있나요, 그리고 그런 일들이 그때 일어나는 일과 상관없이 저절로 일어나는 것처럼 느껴지기도 하나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 가끔은 뭔가 큰 일이랑 연결돼 있는 것 같지 않을 때도 있어요. 그냥 직장에서 마감할 때나 집 부엌에 있을 때, 특별히 화가 난 상태도 아닌데 그럴 수 있어요. 여자 목소리가 제 이름을 부르거나, 계산이 틀렸다고 말하는 게 들리는데, 진짜처럼 들려서 대답을 하고 나서야 아무도 못 들었다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 사실이 아니라는 걸 알면서도, 그렇게 생각할 이유가 없는데도, 그리고 그 믿음이 본인의 삶에서 일어나는 일과 연결되지 않는데도 뭔가를 믿은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네… 직장 관련된 일이 그런 것 같아요. 서버 몇 명이랑 이 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 느낌이 계속 들어요, 마치 실수를 찾는 것처럼요.
-그리고 영수증에 표시가 있거나 뭔가 바뀐 것 같으면, 그게 신호를 남기는 것처럼, 저를 해고시키려는 증거처럼 느껴져요. 남편은 그냥 평범한 식당 실수일 뿐이라고 하고, 저도 그 말이 이해는 되는데, 그래도 그 순간엔 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 특별히 우울하거나 불안하거나 화가 나지 않았을 때 이런 생각이나 믿음이 들었던 때를 떠올릴 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 딱히 화가 나지 않았던, 꽤 평범한 날에도 직장에서 그런 일이 있었어요. 그냥 주문을 입력하고 있는데, 서버 몇 명이랑 그 단골손님이 저를 지켜보고 있는 것 같은 느낌이 들기 시작해요, 제가 실수하기를 기다리는 것처럼요.
-그러고 나서 영수증에 표시가 있거나 뭔가 바뀐 것 같으면, 그걸 저를 위해 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여요. 남편은 그냥 평범한 식당 혼선일 뿐이라고 하는데, 그 순간에는 여전히 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 전혀 증거가 없는데도 다른 사람들이 이상하다거나 이해하기 힘들다고 여길 만한 것을 믿은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 이상하게 들릴 거란 건 아는데, 서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 계속 지켜보고 있다는 생각이 들어요.
-영수증에 작은 표시가 있거나 뭔가 바뀐 것 같으면, 그걸 저한테 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여요. 남편은 그냥 평범한 식당 착오일 뿐이라고 하고, 왜 그렇게 말하는지 이해는 가는데, 막상 그 일이 일어날 때는 저한테는 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 대부분의 사람들이 매우 이상하거나 불가능하다고 여길 만한, 현실에 전혀 근거가 없는 것을 믿은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 그러니까… 외계인 같은 불가능한 얘기는 아닌데, 말로 꺼내놓고 보면 근거가 별로 없다는 느낌은 들어요.
-서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 느낌이 계속 들어요. 그리고 영수증에 작은 표시가 있거나 뭔가 바뀐 것 같으면, 저를 위해 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여요.
-남편은 그냥 평범한 식당 실수나 혼선일 뿐이라고 하고, 그게 더 말이 된다는 것도 알아요. 근데 제가 그 자리에 있을 때는 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 우울하거나 불안하거나 화가 난 상태가 전혀 아닐 때도 사람들이 지켜보고 있다거나 해고시키려 한다는 이런 믿음을 가진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 전혀 우울하거나 불안하거나 그런 상태가 아닐 때도 일어나요. 그러니까 직장에서 평범한 근무를 하다가도, 서버 몇 명이랑 단골손님 한 명이 제가 주문 입력하는 걸 지켜보고 있다는 느낌이 여전히 들어요.
-그러고 나서 영수증에 작은 표시가 있거나 뭔가 이상해 보이면, 그게 저를 위해 남긴 신호처럼, 저를 해고시키려는 증거처럼 받아들여져요. 남편은 그냥 평범한 식당 혼선일 뿐이라고 하고, 아마 사실일 거란 것도 아는데, 그 순간에는 여전히 그걸 믿게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 다른 사람들이 이런 신호를 눈치채지 못하고 남편분도 그냥 평범한 식당 실수일 뿐이라고 논리적으로는 이해하면서도, 마음속 깊은 곳에서는 여전히 본인의 믿음이 절대적으로 사실이고 의심의 여지가 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네… 그 일이 일어나고 있을 때는 마음속 깊은 곳에서 여전히 그게 사실이라고 느끼는 것 같아요.
-남편이 그냥 평범한 식당 일일 뿐이라고 하는 걸 들을 수 있고, 마음 한편으로는 그게 말이 된다는 것도 알아요. 근데 직장에서 영수증에 표시가 있거나 뭔가 바뀐 걸 볼 때는, 일부러 그러는 것처럼 느껴져요—서버들이랑 그 단골손님이 저를 지켜보면서 해고당하도록 몰아가려는 것처럼요. 증명은 못 해도 그냥 넘기기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 사실이 아니라는 명백한 증거를 본 후에도 이런 믿음 중 하나를 계속 붙들고 있었던 때를 떠올릴 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 한번은 서버 중 한 명이 제가 어떻게 주문을 입력하는지 추적하려고 다른 사람들에게 경고하기 위해 영수증에 표시를 했다고 생각한 적이 있어요.
-나중에 남편이 그걸 보더니 그냥 평범한 실수라고, 누가 낙서를 했거나 주문 때문에 뭔가 바꾼 거라고 했어요. 그리고 저도 남편이 무슨 말을 하는지는 이해했어요. 사실 그건 아무것도 증명하지 못했어요.
-근데 그 후에도 저는 계속 생각했어요, 아니야, 그 표시는 이유가 있어서 거기 있었던 거야. 여전히 저를 해고시키려고 몰아가려는 것 같았어요. 한번 눈치채고 나면 그걸 놓아버리기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 영수증의 표시가 그냥 평범한 실수였다는 걸 본 후에도, 그게 실제로 서버들이 본인을 해고시키기 위한 비밀 신호라고 여전히 확신했고, 그 순간에는 다른 설명을 받아들일 수 없었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 그냥 평범한 실수였을 수도 있다는 걸 알아본 후에도, 여전히 뭔가 의미가 있다고 느꼈어요.
-그때는 그게 정말 아무것도 아니라는 걸 받아들일 수가 없었어요. 계속 서버들이 영수증에 그런 작은 신호들을 남기고 있고, 그 단골손님도 지켜보고 있다는 생각이 들었어요, 마치 다들 제가 뭔가 잘못하는 걸 잡아서 해고시키려는 것처럼요. 남편이 평범한 일이라고 말해준 것도 그 생각을 딱히 없애주지는 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 영수증의 표시가 아마도 그냥 평범한 실수였다는 걸 본 후에도, 그게 실제로 서버들이 남긴 비밀 신호라고 여전히 완전히 확신했고, 그게 그냥 사고였을 수도 있다는 게 불가능하게 느껴졌나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네… 그때는 정말 그게 그냥 사고일 수는 없다고 느껴졌어요.
-남편이 아마 그냥 평범한 식당 혼선일 거라고 말했을 때도, 저는 여전히 그 표시가 뭔가 의미가 있다고 확신했어요. 서버들이 영수증에 신호를 남기고 있고, 그 단골손님도 제가 주문 입력하는 걸 지켜보면서 제가 해고당하게 만들려고 뭔가를 증명하려는 것 같았어요. 얘기하고 보니 좀 과하게 들리는 건 아는데, 그 순간에는 저한테 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+배경 서술: 코리나가 서브세이프 매니저 자격증을 준비하면서 저녁 근무 조 팀장을 맡아달라는 요청을 받았을 때, 그 추가된 책임은 평소 여유롭던 식당 업무 루틴을 끊임없는 압박의 원천으로 바꿔 놓았다. 이후 1년 2개월에 걸쳐, 동료와 손님에 대한 초기의 다소 이상한 우려는 고정된 믿음으로 굳어졌고, 그녀는 다른 사람들이 확인할 수 없는 경험에 반응하기 시작했으며, 서비스 도중 행동이 흐트러져 주문, 현금 처리, 마감 절차에 지장을 줄 정도가 되었다. 집에서는 남편이 그녀가 위축되고 의욕을 잃으면서 해변 산책, 정원 가꾸기, 베이킹, 일기 쓰기가 점점 줄어드는 것을 알아챘다. 그녀는 매니저 평가에 실패하고 고용주와의 면담에서 직장과 결혼 생활을 지키기 위해 긴급 외래 평가에 동의한 뒤 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
+        </is>
+      </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
-  누락: 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22.0)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S003_P001__qwen3-235b_kor.xlsx
@@ -849,6 +849,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -886,11 +891,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S003_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2526</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.259</v>
+        <v>0.7564</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
